--- a/RVMD.xlsx
+++ b/RVMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613D24EE-DAA3-46CA-B1E8-4905103FA6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7A1393-E431-4CAA-A92F-176E0F97F636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50170" yWindow="5020" windowWidth="26630" windowHeight="15210" activeTab="1" xr2:uid="{6D08A6DD-AC07-40C1-BFD9-0B3DF43E325A}"/>
+    <workbookView xWindow="20880" yWindow="3490" windowWidth="19050" windowHeight="16100" xr2:uid="{6D08A6DD-AC07-40C1-BFD9-0B3DF43E325A}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -91,9 +91,6 @@
     <t>RMC-5127</t>
   </si>
   <si>
-    <t>Q225</t>
-  </si>
-  <si>
     <t>Brand</t>
   </si>
   <si>
@@ -209,6 +206,9 @@
   </si>
   <si>
     <t>Initiate Q4</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -765,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>54.16</v>
+        <v>187.53</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
@@ -786,10 +786,10 @@
         <v>1</v>
       </c>
       <c r="J3" s="14">
-        <v>188.58328800000001</v>
+        <v>212.596462</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
@@ -804,7 +804,7 @@
       </c>
       <c r="J4" s="14">
         <f>+J2*J3</f>
-        <v>10213.67087808</v>
+        <v>39868.214518860004</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -818,11 +818,11 @@
         <v>3</v>
       </c>
       <c r="J5" s="14">
-        <f>402.438+1734.733</f>
-        <v>2137.1709999999998</v>
+        <f>440.939+1467.145+34.709+4.858</f>
+        <v>1947.6510000000001</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
       </c>
       <c r="J7" s="14">
         <f>+J4-J5+J6</f>
-        <v>8076.4998780799997</v>
+        <v>37920.563518860006</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
@@ -893,18 +893,18 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -912,7 +912,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -920,106 +920,106 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C9" s="17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="C13" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="3:6" ht="13" x14ac:dyDescent="0.3">
       <c r="C17" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="13" x14ac:dyDescent="0.3">
       <c r="C21" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="3:6" x14ac:dyDescent="0.25">
       <c r="D31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1055,49 +1055,49 @@
         <v>2028</v>
       </c>
       <c r="F2">
-        <f>+E2+1</f>
+        <f t="shared" ref="F2:O2" si="0">+E2+1</f>
         <v>2029</v>
       </c>
       <c r="G2">
-        <f>+F2+1</f>
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="H2">
-        <f>+G2+1</f>
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I2">
-        <f>+H2+1</f>
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="J2">
-        <f>+I2+1</f>
+        <f t="shared" si="0"/>
         <v>2033</v>
       </c>
       <c r="K2">
-        <f>+J2+1</f>
+        <f t="shared" si="0"/>
         <v>2034</v>
       </c>
       <c r="L2">
-        <f>+K2+1</f>
+        <f t="shared" si="0"/>
         <v>2035</v>
       </c>
       <c r="M2">
-        <f>+L2+1</f>
+        <f t="shared" si="0"/>
         <v>2036</v>
       </c>
       <c r="N2">
-        <f>+M2+1</f>
+        <f t="shared" si="0"/>
         <v>2037</v>
       </c>
       <c r="O2">
-        <f>+N2+1</f>
+        <f t="shared" si="0"/>
         <v>2038</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="19">
         <v>60000</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="20">
         <v>0.1</v>
@@ -1185,58 +1185,58 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5">
         <f>+C4*C3</f>
         <v>6000</v>
       </c>
       <c r="D5">
-        <f t="shared" ref="D5:O5" si="0">+D4*D3</f>
+        <f t="shared" ref="D5:O5" si="1">+D4*D3</f>
         <v>18000</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30000</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33000</v>
       </c>
       <c r="G5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36000</v>
       </c>
       <c r="H5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>39000</v>
       </c>
       <c r="I5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42000</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="K5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="L5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="N5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
       <c r="O5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45000</v>
       </c>
     </row>
@@ -1286,178 +1286,178 @@
     </row>
     <row r="7" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B7" s="21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="22">
         <f>+C5*C6/1000000</f>
         <v>720</v>
       </c>
       <c r="D7" s="22">
-        <f t="shared" ref="D7:O7" si="1">+D5*D6/1000000</f>
+        <f t="shared" ref="D7:O7" si="2">+D5*D6/1000000</f>
         <v>2160</v>
       </c>
       <c r="E7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3600</v>
       </c>
       <c r="F7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3960</v>
       </c>
       <c r="G7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4320</v>
       </c>
       <c r="H7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4680</v>
       </c>
       <c r="I7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5040</v>
       </c>
       <c r="J7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5400</v>
       </c>
       <c r="K7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5400</v>
       </c>
       <c r="L7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5400</v>
       </c>
       <c r="M7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5400</v>
       </c>
       <c r="N7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5400</v>
       </c>
       <c r="O7" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5400</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <f>+C7*0.1</f>
         <v>72</v>
       </c>
       <c r="D8">
-        <f t="shared" ref="D8:O8" si="2">+D7*0.1</f>
+        <f t="shared" ref="D8:O8" si="3">+D7*0.1</f>
         <v>216</v>
       </c>
       <c r="E8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>360</v>
       </c>
       <c r="F8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>396</v>
       </c>
       <c r="G8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>432</v>
       </c>
       <c r="H8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>468</v>
       </c>
       <c r="I8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>504</v>
       </c>
       <c r="J8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="K8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="L8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="M8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="N8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
       <c r="O8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="19">
         <f>+C7-C8</f>
         <v>648</v>
       </c>
       <c r="D9" s="19">
-        <f t="shared" ref="D9:O9" si="3">+D7-D8</f>
+        <f t="shared" ref="D9:O9" si="4">+D7-D8</f>
         <v>1944</v>
       </c>
       <c r="E9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3240</v>
       </c>
       <c r="F9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3564</v>
       </c>
       <c r="G9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3888</v>
       </c>
       <c r="H9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4212</v>
       </c>
       <c r="I9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4536</v>
       </c>
       <c r="J9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4860</v>
       </c>
       <c r="K9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4860</v>
       </c>
       <c r="L9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4860</v>
       </c>
       <c r="M9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4860</v>
       </c>
       <c r="N9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4860</v>
       </c>
       <c r="O9" s="19">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4860</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>500</v>
@@ -1501,178 +1501,178 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="19">
         <f>+C9-C10</f>
         <v>148</v>
       </c>
       <c r="D11" s="19">
-        <f t="shared" ref="D11:O11" si="4">+D9-D10</f>
+        <f t="shared" ref="D11:O11" si="5">+D9-D10</f>
         <v>1444</v>
       </c>
       <c r="E11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2740</v>
       </c>
       <c r="F11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3064</v>
       </c>
       <c r="G11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3388</v>
       </c>
       <c r="H11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3712</v>
       </c>
       <c r="I11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4036</v>
       </c>
       <c r="J11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4360</v>
       </c>
       <c r="K11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4360</v>
       </c>
       <c r="L11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4360</v>
       </c>
       <c r="M11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4360</v>
       </c>
       <c r="N11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4360</v>
       </c>
       <c r="O11" s="19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4360</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="19">
         <f>+C11*0.15</f>
         <v>22.2</v>
       </c>
       <c r="D12" s="19">
-        <f t="shared" ref="D12:O12" si="5">+D11*0.15</f>
+        <f t="shared" ref="D12:O12" si="6">+D11*0.15</f>
         <v>216.6</v>
       </c>
       <c r="E12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>411</v>
       </c>
       <c r="F12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>459.59999999999997</v>
       </c>
       <c r="G12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>508.2</v>
       </c>
       <c r="H12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>556.79999999999995</v>
       </c>
       <c r="I12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>605.4</v>
       </c>
       <c r="J12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>654</v>
       </c>
       <c r="K12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>654</v>
       </c>
       <c r="L12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>654</v>
       </c>
       <c r="M12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>654</v>
       </c>
       <c r="N12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>654</v>
       </c>
       <c r="O12" s="19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>654</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="19">
         <f>+C11-C12</f>
         <v>125.8</v>
       </c>
       <c r="D13" s="19">
-        <f t="shared" ref="D13:O13" si="6">+D11-D12</f>
+        <f t="shared" ref="D13:O13" si="7">+D11-D12</f>
         <v>1227.4000000000001</v>
       </c>
       <c r="E13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2329</v>
       </c>
       <c r="F13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2604.4</v>
       </c>
       <c r="G13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2879.8</v>
       </c>
       <c r="H13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3155.2</v>
       </c>
       <c r="I13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3430.6</v>
       </c>
       <c r="J13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3706</v>
       </c>
       <c r="K13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3706</v>
       </c>
       <c r="L13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3706</v>
       </c>
       <c r="M13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3706</v>
       </c>
       <c r="N13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3706</v>
       </c>
       <c r="O13" s="19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3706</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="20">
         <v>0.1</v>
@@ -1680,7 +1680,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="19">
         <f>NPV(C15,C13:O13)</f>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="23">
         <f>+C16/189</f>
